--- a/extenbooks/XS1103.xlsx
+++ b/extenbooks/XS1103.xlsx
@@ -447,11 +447,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,7 +463,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Shaikh &amp; Tonak 1987, units=rate</t>
+          <t>S&amp;T 1994 Table N.2 (Candidate A), units=rate</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>S604/S617 (includes excluded indirect taxes), units=rate</t>
         </is>
       </c>
     </row>
@@ -475,6 +481,11 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>XS1103-A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>XS1103-RECON-A</t>
         </is>
       </c>
     </row>
@@ -483,6 +494,9 @@
         <v>1952</v>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.270987012987013</v>
       </c>
     </row>
@@ -491,6 +505,9 @@
         <v>1953</v>
       </c>
       <c r="B4" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>0.2685086968919304</v>
       </c>
     </row>
@@ -499,6 +516,9 @@
         <v>1954</v>
       </c>
       <c r="B5" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>0.2614973491904284</v>
       </c>
     </row>
@@ -507,6 +527,9 @@
         <v>1955</v>
       </c>
       <c r="B6" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>0.2658879249291785</v>
       </c>
     </row>
@@ -515,6 +538,9 @@
         <v>1956</v>
       </c>
       <c r="B7" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>0.2715628830595734</v>
       </c>
     </row>
@@ -523,6 +549,9 @@
         <v>1957</v>
       </c>
       <c r="B8" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>0.277747905027933</v>
       </c>
     </row>
@@ -531,6 +560,9 @@
         <v>1958</v>
       </c>
       <c r="B9" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>0.2753826609177702</v>
       </c>
     </row>
@@ -539,6 +571,9 @@
         <v>1959</v>
       </c>
       <c r="B10" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>0.2857690940122315</v>
       </c>
     </row>
@@ -547,6 +582,9 @@
         <v>1960</v>
       </c>
       <c r="B11" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>0.3008009168745365</v>
       </c>
     </row>
@@ -555,6 +593,9 @@
         <v>1961</v>
       </c>
       <c r="B12" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>0.3016733211153292</v>
       </c>
     </row>
@@ -563,6 +604,9 @@
         <v>1962</v>
       </c>
       <c r="B13" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>0.3079381222894142</v>
       </c>
     </row>
@@ -571,6 +615,9 @@
         <v>1963</v>
       </c>
       <c r="B14" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>0.3141508451030331</v>
       </c>
     </row>
@@ -579,6 +626,9 @@
         <v>1964</v>
       </c>
       <c r="B15" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>0.2993579341761233</v>
       </c>
     </row>
@@ -587,6 +637,9 @@
         <v>1965</v>
       </c>
       <c r="B16" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>0.2978980541243559</v>
       </c>
     </row>
@@ -595,6 +648,9 @@
         <v>1966</v>
       </c>
       <c r="B17" s="3" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>0.3103097415058133</v>
       </c>
     </row>
@@ -603,6 +659,9 @@
         <v>1967</v>
       </c>
       <c r="B18" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>0.3161133075370121</v>
       </c>
     </row>
@@ -611,6 +670,9 @@
         <v>1968</v>
       </c>
       <c r="B19" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>0.3283482619301722</v>
       </c>
     </row>
@@ -619,6 +681,9 @@
         <v>1969</v>
       </c>
       <c r="B20" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>0.3424499887615194</v>
       </c>
     </row>
@@ -627,6 +692,9 @@
         <v>1970</v>
       </c>
       <c r="B21" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>0.3313000371993724</v>
       </c>
     </row>
@@ -635,6 +703,9 @@
         <v>1971</v>
       </c>
       <c r="B22" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>0.3269002229400792</v>
       </c>
     </row>
@@ -643,6 +714,9 @@
         <v>1972</v>
       </c>
       <c r="B23" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>0.3389072482925754</v>
       </c>
     </row>
@@ -651,6 +725,9 @@
         <v>1973</v>
       </c>
       <c r="B24" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>0.3401767897346308</v>
       </c>
     </row>
@@ -659,6 +736,9 @@
         <v>1974</v>
       </c>
       <c r="B25" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>0.342602519943004</v>
       </c>
     </row>
@@ -667,6 +747,9 @@
         <v>1975</v>
       </c>
       <c r="B26" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>0.3285492473753004</v>
       </c>
     </row>
@@ -675,6 +758,9 @@
         <v>1976</v>
       </c>
       <c r="B27" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>0.3337471286099164</v>
       </c>
     </row>
@@ -683,6 +769,9 @@
         <v>1977</v>
       </c>
       <c r="B28" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>0.3364838265540276</v>
       </c>
     </row>
@@ -691,6 +780,9 @@
         <v>1978</v>
       </c>
       <c r="B29" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>0.3356307034899904</v>
       </c>
     </row>
@@ -699,6 +791,9 @@
         <v>1979</v>
       </c>
       <c r="B30" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>0.3375544454874614</v>
       </c>
     </row>
@@ -707,6 +802,9 @@
         <v>1980</v>
       </c>
       <c r="B31" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>0.3353898743758469</v>
       </c>
     </row>
@@ -715,6 +813,9 @@
         <v>1981</v>
       </c>
       <c r="B32" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>0.3511107053739882</v>
       </c>
     </row>
@@ -723,6 +824,9 @@
         <v>1982</v>
       </c>
       <c r="B33" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>0.3438793713719383</v>
       </c>
     </row>
@@ -731,6 +835,9 @@
         <v>1983</v>
       </c>
       <c r="B34" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>0.340359528876132</v>
       </c>
     </row>
@@ -739,6 +846,9 @@
         <v>1984</v>
       </c>
       <c r="B35" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>0.3420168659352374</v>
       </c>
     </row>
@@ -747,6 +857,9 @@
         <v>1985</v>
       </c>
       <c r="B36" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>0.3493316297438279</v>
       </c>
     </row>
@@ -755,6 +868,9 @@
         <v>1986</v>
       </c>
       <c r="B37" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>0.3504453691168273</v>
       </c>
     </row>
@@ -763,6 +879,9 @@
         <v>1987</v>
       </c>
       <c r="B38" s="3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>0.3583535732877221</v>
       </c>
     </row>
@@ -771,6 +890,9 @@
         <v>1988</v>
       </c>
       <c r="B39" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>0.3566599428591099</v>
       </c>
     </row>
@@ -779,6 +901,9 @@
         <v>1989</v>
       </c>
       <c r="B40" s="3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>0.3627443325755116</v>
       </c>
     </row>
@@ -793,7 +918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -965,56 +1090,60 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Shaikh &amp; Tonak 1987</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+          <t>S&amp;T 1994 Table N.2 (Candidate A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>XS1103-RECON-A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>S604/S617 (includes excluded indirect taxes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t># XS1103 — Social Tax Rate (Shaikh &amp; Tonak 1987)</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t># XS1103 — Social Tax Rate (Shaikh &amp; Tonak 1987)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>## Series</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>## Series</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>- **SID**: XS1103</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>- **Name**: Social Tax Rate (ST 1987)</t>
+          <t>- **SID**: XS1103</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1151,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>- **Study**: `study_02_st_1987` — Shaikh &amp; Tonak (1987) "The Welfare State and the Myth of the Social Wage" in Cherry et al. eds., *The Imperiled Economy*, Book I, pp.184-194</t>
+          <t>- **Name**: Social Tax Rate (ST 1987)</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1159,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>- **Chapter**: ES-prefix follow-up study (registry chapter index 11; book equivalent is the 1987 ST paper, not the 1994 book)</t>
+          <t>- **Study**: `study_02_st_1987` — Shaikh &amp; Tonak (1987) "The Welfare State and the Myth of the Social Wage" in Cherry et al. eds., *The Imperiled Economy*, Book I, pp.184-194</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1167,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>- **Status**: book_period_validated</t>
+          <t>- **Chapter**: ES-prefix follow-up study (registry chapter index 11; book equivalent is the 1987 ST paper, not the 1994 book)</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1175,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>- **Status note**: (1952-1985 annual; Wave-2 / Stage-4 extension to 1986-2024 pending NIPA Group I/II reconstruction)</t>
+          <t>- **Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -1054,87 +1183,87 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>- **Units**: ratio (dimensionless)</t>
+          <t>- **Status note**: (1952-1985 annual; Wave-2 / Stage-4 extension to 1986-2024 pending NIPA Group I/II reconstruction)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>- **Units**: ratio (dimensionless)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>## Methodology</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>## Methodology</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>XS1103 implements the comprehensive social tax rate defined in Shaikh &amp; Tonak (1987). The construction divides total taxes paid by workers (`S604 = T_w`) by total employee compensation (`S617 = EC`), yielding a dimensionless rate. The verbatim primary anchor for the numerator is **"Taxes (from workers): = Group I (Social Security contributions from employee compensation) + Labor's share of Group II (personal taxes)"** (Shaikh &amp; Tonak 1987, Empirical Methodology, p.187). The data source is the book's Appendix Table 1 (p.191, the 1964 illustration) and Table 2 (p.192, the full 1952-1985 annual taxes-paid-by-labor column), cross-checked against BEA *Survey of Current Business* 1981 tables at pp.121, 123, 129, 134, and 170.</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>XS1103 implements the comprehensive social tax rate defined in Shaikh &amp; Tonak (1987). The construction divides total taxes paid by workers (`S604 = T_w`) by total employee compensation (`S617 = EC`), yielding a dimensionless rate. The verbatim primary anchor for the numerator is **"Taxes (from workers): = Group I (Social Security contributions from employee compensation) + Labor's share of Group II (personal taxes)"** (Shaikh &amp; Tonak 1987, Empirical Methodology, p.187). The data source is the book's Appendix Table 1 (p.191, the 1964 illustration) and Table 2 (p.192, the full 1952-1985 annual taxes-paid-by-labor column), cross-checked against BEA *Survey of Current Business* 1981 tables at pp.121, 123, 129, 134, and 170.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>The numerator `T_w` aggregates two groups. Group I (100% from workers — flows directly from employee compensation) comprises: Employer + Employee Contributions for Social Insurance, Other Labor Income (pension contributions), and the small net receipts from government-administered lotteries and parimutuels (treated as a positive net tax, sign-inverted from BEA's listing because the net receipts are consistently positive to the state). Group II (allocated by labor share = total labor income ÷ personal income) comprises: federal and state personal income taxes, motor vehicle licenses, the home-owner portion of property taxes, and miscellaneous other taxes and non-taxes. The 1964 illustration in Appendix Table 1 yields: Group I (28.66 + 0.002 = 28.662) plus Group II (36.51 + 2.60 + 0.78 + 5.99 = 45.88) = total `T_w = 74.52B` in 1964. Corporate profit taxes, indirect business taxes, and estate and gift taxes are excluded as not levied on workers. The denominator (`EC`) is computed at the cost-to-capitalists level — wages and benefits plus employer Social Security contributions plus Other Labor Income — so that the employer SS contribution appears in both numerator and denominator, correctly reflecting that it is a labor cost workers bear via reduced take-home pay. The verbatim trajectory anchor is **"Tax Rate: 1952: ~0.17 (17%) … Rises slowly and steadily throughout period … 1968: ~0.22 (22%) … 1975: ~0.24 (24%) … 1984: ~0.31 (31%) … By 1984: Reaches all-time high (41% higher than 1966)"** (Shaikh &amp; Tonak 1987, Figure 2 description, p.188).</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>The numerator `T_w` aggregates two groups. Group I (100% from workers — flows directly from employee compensation) comprises: Employer + Employee Contributions for Social Insurance, Other Labor Income (pension contributions), and the small net receipts from government-administered lotteries and parimutuels (treated as a positive net tax, sign-inverted from BEA's listing because the net receipts are consistently positive to the state). Group II (allocated by labor share = total labor income ÷ personal income) comprises: federal and state personal income taxes, motor vehicle licenses, the home-owner portion of property taxes, and miscellaneous other taxes and non-taxes. The 1964 illustration in Appendix Table 1 yields: Group I (28.66 + 0.002 = 28.662) plus Group II (36.51 + 2.60 + 0.78 + 5.99 = 45.88) = total `T_w = 74.52B` in 1964. Corporate profit taxes, indirect business taxes, and estate and gift taxes are excluded as not levied on workers. The denominator (`EC`) is computed at the cost-to-capitalists level — wages and benefits plus employer Social Security contributions plus Other Labor Income — so that the employer SS contribution appears in both numerator and denominator, correctly reflecting that it is a labor cost workers bear via reduced take-home pay. The verbatim trajectory anchor is **"Tax Rate: 1952: ~0.17 (17%) … Rises slowly and steadily throughout period … 1968: ~0.22 (22%) … 1975: ~0.24 (24%) … 1984: ~0.31 (31%) … By 1984: Reaches all-time high (41% higher than 1966)"** (Shaikh &amp; Tonak 1987, Figure 2 description, p.188).</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>The transformation produces a monotonically rising rate over 1952-1985 (~17% → ~31%), driven primarily by Social Security expansion rather than income-tax policy. The Reagan-era income tax cuts were offset by continuing growth in social security contributions, so by 1985 the rate reached 41% above its 1966 level despite income-tax rate reductions — illustrating that the social-security component dominates the long-run trend. The substantive interpretive thrust the rising tax rate supports is the rebuttal of the Bowles &amp; Gintis "rising social wage" thesis: **"Arguments such as those of Bowles and Gintis, which claim that 'there has been a substantial redistribution from capital to labor' over the postwar period, and which trace the current economic crisis back to a supposed increased social wage, appear to be quite ill-founded."** (Shaikh &amp; Tonak 1987, p.187). Validation runs against book benchmarks in Figure 2 and Table 2 (1952 ≈ 0.17, 1966 ≈ 0.22, 1975 ≈ 0.24, 1984 ≈ 0.31) within the rate-series tolerance class; the V03 validator additionally enforces the expected range `[0.0, 0.3]`. Comparison with BLS spendable-earnings-derived series (Bowles &amp; Gintis) is intentionally not used as validation because BLS omits state and local taxes — Bowles &amp; Gintis's 1977 tax estimate was $10/week vs Tonak's $30.42/week, a two-thirds underestimate documented in note 5 (p.193).</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>The transformation produces a monotonically rising rate over 1952-1985 (~17% → ~31%), driven primarily by Social Security expansion rather than income-tax policy. The Reagan-era income tax cuts were offset by continuing growth in social security contributions, so by 1985 the rate reached 41% above its 1966 level despite income-tax rate reductions — illustrating that the social-security component dominates the long-run trend. The substantive interpretive thrust the rising tax rate supports is the rebuttal of the Bowles &amp; Gintis "rising social wage" thesis: **"Arguments such as those of Bowles and Gintis, which claim that 'there has been a substantial redistribution from capital to labor' over the postwar period, and which trace the current economic crisis back to a supposed increased social wage, appear to be quite ill-founded."** (Shaikh &amp; Tonak 1987, p.187). Validation runs against book benchmarks in Figure 2 and Table 2 (1952 ≈ 0.17, 1966 ≈ 0.22, 1975 ≈ 0.24, 1984 ≈ 0.31) within the rate-series tolerance class; the V03 validator additionally enforces the expected range `[0.0, 0.3]`. Comparison with BLS spendable-earnings-derived series (Bowles &amp; Gintis) is intentionally not used as validation because BLS omits state and local taxes — Bowles &amp; Gintis's 1977 tax estimate was $10/week vs Tonak's $30.42/week, a two-thirds underestimate documented in note 5 (p.193).</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>## Sources</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>## Sources</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>- KB chunks: `Technical/Knowledge_Base/external_papers/productive_labor/1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md` (full ST 1987 paper extraction)</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>- Book tables: ST 1987 Appendix Table 1 (1964 illustration, p.191); ST 1987 Table 2 (taxes column, 1952-1985 annual, p.192); ST 1987 Figure 2 (tax rate trajectory, p.188); ST 1987 Figure 1 (broader social-wage decomposition)</t>
+          <t>- KB chunks: `Technical/Knowledge_Base/external_papers/productive_labor/1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md` (full ST 1987 paper extraction)</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1271,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>- External sources: BEA Survey of Current Business 1981, tables at pp.121, 123, 129, 134 (tax data); BEA SCB 1981 p.170 (lotteries/parimutuels)</t>
+          <t>- Book tables: ST 1987 Appendix Table 1 (1964 illustration, p.191); ST 1987 Table 2 (taxes column, 1952-1985 annual, p.192); ST 1987 Figure 2 (tax rate trajectory, p.188); ST 1987 Figure 1 (broader social-wage decomposition)</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1279,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>- Upstream series: S604 (taxes paid by workers T_w), S617 (employee compensation EC)</t>
+          <t>- External sources: BEA Survey of Current Business 1981, tables at pp.121, 123, 129, 134 (tax data); BEA SCB 1981 p.170 (lotteries/parimutuels)</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1287,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>- Companion ES series in the same study: XS1101 (benefits to workers B_w), XS1102 (government transfers G_w), and XS1001/XS1002 (related)</t>
+          <t>- Upstream series: S604 (taxes paid by workers T_w), S617 (employee compensation EC)</t>
         </is>
       </c>
     </row>
@@ -1166,39 +1295,39 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>- Related: Tonak (1984) PhD dissertation "A Conceptualization of State Revenues and Expenditures U.S.: 1952-1980", UMI Order #9414212 — the underlying comprehensive tax accounting framework</t>
+          <t>- Companion ES series in the same study: XS1101 (benefits to workers B_w), XS1102 (government transfers G_w), and XS1001/XS1002 (related)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>- Related: Tonak (1984) PhD dissertation "A Conceptualization of State Revenues and Expenditures U.S.: 1952-1980", UMI Order #9414212 — the underlying comprehensive tax accounting framework</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>## Reference values</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>## Reference values</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>- 34 annual observations 1952-1985</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>- Figure 2 / Table 2 benchmark trajectory: 1952 ≈ 0.17, 1966 ≈ 0.22, 1975 ≈ 0.24, 1984 ≈ 0.31</t>
+          <t>- 34 annual observations 1952-1985</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1335,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>- Absolute dollar values from Table 2: 1952=34.58B, 1964=74.52B, 1975=241.70B, 1985=705.27B</t>
+          <t>- Figure 2 / Table 2 benchmark trajectory: 1952 ≈ 0.17, 1966 ≈ 0.22, 1975 ≈ 0.24, 1984 ≈ 0.31</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1343,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>- 1984 peak is **41% higher than 1966** (the all-time high in the book period)</t>
+          <t>- Absolute dollar values from Table 2: 1952=34.58B, 1964=74.52B, 1975=241.70B, 1985=705.27B</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1351,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>- Validator `expected_range`: **[0.0, 0.3]** (registry; share_series tolerance class)</t>
+          <t>- 1984 peak is **41% higher than 1966** (the all-time high in the book period)</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1359,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>- Direction: monotonically rising throughout 1952-1985 (PASS)</t>
+          <t>- Validator `expected_range`: **[0.0, 0.3]** (registry; share_series tolerance class)</t>
         </is>
       </c>
     </row>
@@ -1238,39 +1367,39 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>- 1964 illustration breakdown (Appendix Table 1): Group I = 28.662B, Group II = 45.88B, total T_w = 74.52B</t>
+          <t>- Direction: monotonically rising throughout 1952-1985 (PASS)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>- 1964 illustration breakdown (Appendix Table 1): Group I = 28.662B, Group II = 45.88B, total T_w = 74.52B</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>## Known issues</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>## Known issues</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>- **Property tax coverage restricted to home-owner portion only** — renters' indirect tax burden (paid via rent) is excluded by framework design (the framework excludes tax shifting); XS1103 therefore likely understates the full property-tax burden on workers who rent</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>- **BLS spendable-earnings comparison will show XS1103 much higher** — BLS omits state and local taxes (Bowles &amp; Gintis's $10/week 1977 estimate vs Tonak's $30.42/week, a two-thirds underestimate per note 5)</t>
+          <t>- **Property tax coverage restricted to home-owner portion only** — renters' indirect tax burden (paid via rent) is excluded by framework design (the framework excludes tax shifting); XS1103 therefore likely understates the full property-tax burden on workers who rent</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1407,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>- **Employer social security contribution is counted in both EC (denominator) and T_w (numerator)** — this is methodologically correct per Note 8 (pp.193-194) but may appear to inflate the rate to readers unfamiliar with the cost-to-capitalists EC definition</t>
+          <t>- **BLS spendable-earnings comparison will show XS1103 much higher** — BLS omits state and local taxes (Bowles &amp; Gintis's $10/week 1977 estimate vs Tonak's $30.42/week, a two-thirds underestimate per note 5)</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1415,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>- **Lotteries/parimutuels is a very small Group I addition** treated as net tax (sign-inverted from BEA listing — BEA lists as expenditure but net is consistently positive)</t>
+          <t>- **Employer social security contribution is counted in both EC (denominator) and T_w (numerator)** — this is methodologically correct per Note 8 (pp.193-194) but may appear to inflate the rate to readers unfamiliar with the cost-to-capitalists EC definition</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1423,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>- **Extension to 1986-2024 pending** Stage-4 NIPA Group I/II reconstruction (would require building a continuous concordance from current BEA NIPA tables to the 1987 paper's tax classification)</t>
+          <t>- **Lotteries/parimutuels is a very small Group I addition** treated as net tax (sign-inverted from BEA listing — BEA lists as expenditure but net is consistently positive)</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1431,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>- **No EPR yet authored** for XS1103 (Stage 4 work)</t>
+          <t>- **Extension to 1986-2024 pending** Stage-4 NIPA Group I/II reconstruction (would require building a continuous concordance from current BEA NIPA tables to the 1987 paper's tax classification)</t>
         </is>
       </c>
     </row>
@@ -1310,39 +1439,39 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>- **Inherits S604 status**: if S604 contains synthetic or estimated rows, XS1103 inherits that status — [internal-decision-record] (No Synthetic Data Policy, 2026-05-03) does not currently list XS1103 among the five series requiring remediation, but the dependency should be re-checked after any S604 revision</t>
+          <t>- **No EPR yet authored** for XS1103 (Stage 4 work)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>- **Inherits S604 status**: if S604 contains synthetic or estimated rows, XS1103 inherits that status — [internal-decision-record] (No Synthetic Data Policy, 2026-05-03) does not currently list XS1103 among the five series requiring remediation, but the dependency should be re-checked after any S604 revision</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>## Cross-references</t>
-        </is>
-      </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>## Cross-references</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>- Upstream: S604 (taxes paid by workers), S617 (employee compensation)</t>
-        </is>
-      </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>- Companion ES series (same study): XS1101 (benefits B_w), XS1102 (government transfers G_w), XS1001, XS1002</t>
+          <t>- Upstream: S604 (taxes paid by workers), S617 (employee compensation)</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1479,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>- Downstream: S607 (Net Social Wage NSW = B_w + G_w − T_w; XS1103's numerator is the T_w component); S608 (NSW/V* ratio) — both used in S901 summary table</t>
+          <t>- Companion ES series (same study): XS1101 (benefits B_w), XS1102 (government transfers G_w), XS1001, XS1002</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1487,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>- Related external: Tonak (1984) PhD dissertation (underlying tax accounting framework); BEA Survey of Current Business 1981; Bowles &amp; Gintis (1985) — the "rising social wage" thesis XS1103's rising tax-rate finding refutes; Miller (1986) — the tax-incidence / tax-shifting framework ST 1987 explicitly distinguishes itself from</t>
+          <t>- Downstream: S607 (Net Social Wage NSW = B_w + G_w − T_w; XS1103's numerator is the T_w component); S608 (NSW/V* ratio) — both used in S901 summary table</t>
         </is>
       </c>
     </row>
@@ -1366,39 +1495,39 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>- Related project DPRs: XS1101 (benefits side of the same NSW decomposition); XS001 (social burden rate — different decomposition of the same fiscal-burden question)</t>
+          <t>- Related external: Tonak (1984) PhD dissertation (underlying tax accounting framework); BEA Survey of Current Business 1981; Bowles &amp; Gintis (1985) — the "rising social wage" thesis XS1103's rising tax-rate finding refutes; Miller (1986) — the tax-incidence / tax-shifting framework ST 1987 explicitly distinguishes itself from</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>- Related project DPRs: XS1101 (benefits side of the same NSW decomposition); XS001 (social burden rate — different decomposition of the same fiscal-burden question)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>## Provenance trail</t>
-        </is>
-      </c>
+      <c r="B76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>## Provenance trail</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>- **Original research**: `Technical/research/XS1103_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/N1103_research.json` on 2026-05-14; verbatim quotes added 2026-05-19 by `D4_es_ch10_13_backfill`</t>
-        </is>
-      </c>
+      <c r="B78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); prior version of this DPR (pre-cohort-1) was a short stub with one methodology paragraph; this enrichment adds full 7-section structure with sources, reference values, known issues, cross-references; sources read = research JSON + ST 1987 full transcription + registry entry</t>
+          <t>- **Original research**: `Technical/research/XS1103_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/N1103_research.json` on 2026-05-14; verbatim quotes added 2026-05-19 by `D4_es_ch10_13_backfill`</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1535,67 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
+          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); prior version of this DPR (pre-cohort-1) was a short stub with one methodology paragraph; this enrichment adds full 7-section structure with sources, reference values, known issues, cross-references; sources read = research JSON + ST 1987 full transcription + registry entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>- **Anu Framework stage**: Stage 3 INGESTION (cohort 1, failing chapters); ingestion gate IDs P31/P32</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>## D3 book-faithful adoption (2026-07-02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>**XS1103-A is now book Table N.2 T1/EC verbatim** (V03 5/5; was reconstruction 0/5). The excluded indirect/sales-excise tax term now lives ONLY in the **XS1103-RECON-A** / S604 comparison arm (resolves WP-B-DIV-S604-INDIRECT on the primary).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>&gt; Decision: ADOPT NSW Candidate A (Appendix N Tables N.1/N.2 verbatim, 1952-1989) as book-period primary; BEA-API reconstruction becomes the labeled comparison/extension arm. Nothing deleted (.pre_d3 backups + -RECON subseries). See Handoffs/REVIEW_2026-07/D3_REGISTRY_PATCHES.json + D3_DIV_PATCHES.json.</t>
         </is>
       </c>
     </row>
@@ -1898,10 +2087,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1942,17 +2131,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S604, BEA_NIPA</t>
+          <t>S604, S617</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>XS1103-COMBINED</t>
+          <t>XS1103-A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>T_w / EC</t>
+          <t>XS1103 = T_w/EC = S604/S617</t>
         </is>
       </c>
     </row>
@@ -1986,7 +2175,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"1952": 0.17, "1968": 0.22, "1975": 0.24, "1984": 0.31}</t>
+          <t>{"1952": 0.18, "1964": 0.21, "1971": 0.25, "1980": 0.3, "1989": 0.32}</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS1103.xlsx
+++ b/extenbooks/XS1103.xlsx
@@ -1527,7 +1527,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>- **Original research**: `Technical/research/XS1103_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/N1103_research.json` on 2026-05-14; verbatim quotes added 2026-05-19 by `D4_es_ch10_13_backfill`</t>
+          <t>- **Original research**: `Technical/research/XS1103_research.json`, researcher `agent`, 2026-05-06; ported from `predecessor-build/research/N1103_research.json` on 2026-05-14; verbatim quotes added 2026-05-19 by `D4_es_ch10_13_backfill`</t>
         </is>
       </c>
     </row>
